--- a/reports/Debug-purgatory-20260104/For The Day (Prior Year)_Visits.xlsx
+++ b/reports/Debug-purgatory-20260104/For The Day (Prior Year)_Visits.xlsx
@@ -448,7 +448,7 @@
         <v>45662</v>
       </c>
       <c r="C3" s="2">
-        <v>154</v>
+        <v>11</v>
       </c>
       <c r="D3" s="2" t="s">
         <v>5</v>
@@ -462,7 +462,7 @@
         <v>45662</v>
       </c>
       <c r="C4" s="2">
-        <v>11</v>
+        <v>154</v>
       </c>
       <c r="D4" s="2" t="s">
         <v>5</v>
@@ -476,7 +476,7 @@
         <v>45662</v>
       </c>
       <c r="C5" s="2">
-        <v>1</v>
+        <v>18</v>
       </c>
       <c r="D5" s="2" t="s">
         <v>5</v>
@@ -490,7 +490,7 @@
         <v>45662</v>
       </c>
       <c r="C6" s="2">
-        <v>3</v>
+        <v>18</v>
       </c>
       <c r="D6" s="2" t="s">
         <v>5</v>
@@ -504,10 +504,10 @@
         <v>45662</v>
       </c>
       <c r="C7" s="2">
-        <v>60</v>
+        <v>1</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -518,10 +518,10 @@
         <v>45662</v>
       </c>
       <c r="C8" s="2">
-        <v>1125</v>
+        <v>3</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -532,10 +532,10 @@
         <v>45662</v>
       </c>
       <c r="C9" s="2">
-        <v>288</v>
+        <v>60</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -546,10 +546,10 @@
         <v>45662</v>
       </c>
       <c r="C10" s="2">
-        <v>2295</v>
+        <v>1125</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -560,10 +560,10 @@
         <v>45662</v>
       </c>
       <c r="C11" s="2">
-        <v>1</v>
+        <v>288</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -574,7 +574,7 @@
         <v>45662</v>
       </c>
       <c r="C12" s="2">
-        <v>83</v>
+        <v>2295</v>
       </c>
       <c r="D12" s="2" t="s">
         <v>5</v>
@@ -588,7 +588,7 @@
         <v>45662</v>
       </c>
       <c r="C13" s="2">
-        <v>18</v>
+        <v>1</v>
       </c>
       <c r="D13" s="2" t="s">
         <v>5</v>
@@ -602,7 +602,7 @@
         <v>45662</v>
       </c>
       <c r="C14" s="2">
-        <v>18</v>
+        <v>83</v>
       </c>
       <c r="D14" s="2" t="s">
         <v>5</v>
